--- a/12602788.xlsx
+++ b/12602788.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\Desktop\CAP 776\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -240,6 +240,9 @@
   <si>
     <t>High-energy weekend; went for trip too shimla</t>
   </si>
+  <si>
+    <t>Weekend routine was mostly rest,  phone and also did packing for trip.</t>
+  </si>
 </sst>
 </file>
 
@@ -402,7 +405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -432,6 +435,9 @@
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -440,8 +446,8 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -927,74 +933,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="16">
         <v>12602788</v>
       </c>
-      <c r="G2" s="16"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="16"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="16"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
     </row>
     <row r="5" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1040,7 +1046,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>46241</v>
       </c>
@@ -1082,11 +1088,11 @@
       <c r="M6" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="24" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
         <v>46242</v>
       </c>
@@ -1132,7 +1138,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>46243</v>
       </c>
@@ -1178,7 +1184,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
         <v>46244</v>
       </c>
@@ -1224,7 +1230,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>46245</v>
       </c>
@@ -1270,7 +1276,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
         <v>46246</v>
       </c>
@@ -1316,7 +1322,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>46247</v>
       </c>
@@ -1362,7 +1368,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14">
         <v>46248</v>
       </c>
@@ -1408,7 +1414,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>46249</v>
       </c>
@@ -1454,7 +1460,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
         <v>46250</v>
       </c>
@@ -1500,7 +1506,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>46251</v>
       </c>
@@ -1546,7 +1552,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14">
         <v>46252</v>
       </c>
@@ -1592,7 +1598,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>46253</v>
       </c>
@@ -1638,7 +1644,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14">
         <v>46254</v>
       </c>
@@ -1684,7 +1690,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
         <v>46255</v>
       </c>
@@ -1730,7 +1736,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14">
         <v>46256</v>
       </c>
@@ -1776,7 +1782,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <v>46257</v>
       </c>
@@ -1822,7 +1828,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
         <v>46258</v>
       </c>
@@ -1868,7 +1874,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
         <v>46259</v>
       </c>
@@ -1914,7 +1920,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14">
         <v>46260</v>
       </c>
@@ -1960,7 +1966,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
         <v>46261</v>
       </c>
@@ -2006,7 +2012,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14">
         <v>46262</v>
       </c>
@@ -2052,7 +2058,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
         <v>46263</v>
       </c>
@@ -2098,7 +2104,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="14">
         <v>46264</v>
       </c>
@@ -2144,7 +2150,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14">
         <v>46265</v>
       </c>
@@ -2190,7 +2196,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14">
         <v>46266</v>
       </c>
@@ -2236,7 +2242,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14">
         <v>46267</v>
       </c>
@@ -2282,7 +2288,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14">
         <v>46268</v>
       </c>
@@ -2328,7 +2334,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14">
         <v>46269</v>
       </c>
@@ -2374,7 +2380,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14">
         <v>46270</v>
       </c>
@@ -2420,7 +2426,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14">
         <v>46271</v>
       </c>
@@ -2466,7 +2472,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="14">
         <v>46272</v>
       </c>
@@ -2512,7 +2518,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="14">
         <v>46273</v>
       </c>
@@ -2538,11 +2544,11 @@
         <v>210</v>
       </c>
       <c r="I38" s="10">
-        <f t="shared" ref="I38:I69" si="2">IF(SUM(B38:F38,H38)=0,"",SUM(B38:F38,H38))</f>
+        <f t="shared" ref="I38:I60" si="2">IF(SUM(B38:F38,H38)=0,"",SUM(B38:F38,H38))</f>
         <v>1075</v>
       </c>
       <c r="J38" s="10">
-        <f t="shared" ref="J38:J69" si="3">IF(I38="","",1440-I38)</f>
+        <f t="shared" ref="J38:J60" si="3">IF(I38="","",1440-I38)</f>
         <v>365</v>
       </c>
       <c r="K38" s="11" t="s">
@@ -2558,7 +2564,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14">
         <v>46274</v>
       </c>
@@ -2604,7 +2610,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="14">
         <v>46275</v>
       </c>
@@ -2638,7 +2644,7 @@
         <v>415</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L40" s="11" t="s">
         <v>59</v>
@@ -2650,7 +2656,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="14">
         <v>46276</v>
       </c>
@@ -2684,7 +2690,7 @@
         <v>415</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L41" s="11" t="s">
         <v>59</v>
@@ -2696,7 +2702,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="14">
         <v>46277</v>
       </c>
@@ -2730,7 +2736,7 @@
         <v>440</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L42" s="11" t="s">
         <v>56</v>
@@ -2742,7 +2748,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14">
         <v>46278</v>
       </c>
@@ -2788,7 +2794,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14">
         <v>46279</v>
       </c>
@@ -2834,7 +2840,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14">
         <v>46280</v>
       </c>
@@ -2880,7 +2886,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14">
         <v>46281</v>
       </c>
@@ -2926,7 +2932,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="14">
         <v>46282</v>
       </c>
@@ -2972,7 +2978,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="14">
         <v>46283</v>
       </c>
@@ -3018,7 +3024,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="14">
         <v>46284</v>
       </c>
@@ -3041,15 +3047,15 @@
         <v>0</v>
       </c>
       <c r="H49" s="9">
-        <v>540</v>
+        <v>640</v>
       </c>
       <c r="I49" s="10">
         <f t="shared" si="2"/>
-        <v>1135</v>
+        <v>1235</v>
       </c>
       <c r="J49" s="10">
         <f t="shared" si="3"/>
-        <v>305</v>
+        <v>205</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>53</v>
@@ -3061,10 +3067,10 @@
         <v>53</v>
       </c>
       <c r="N49" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="14">
         <v>46285</v>
       </c>
@@ -3075,10 +3081,10 @@
         <v>90</v>
       </c>
       <c r="D50" s="9">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E50" s="9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F50" s="9">
         <v>0</v>
@@ -3087,15 +3093,15 @@
         <v>0</v>
       </c>
       <c r="H50" s="9">
-        <v>540</v>
+        <v>740</v>
       </c>
       <c r="I50" s="10">
         <f t="shared" si="2"/>
-        <v>1235</v>
+        <v>1340</v>
       </c>
       <c r="J50" s="10">
         <f t="shared" si="3"/>
-        <v>205</v>
+        <v>100</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>61</v>
@@ -3110,7 +3116,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="14">
         <v>46286</v>
       </c>
@@ -3121,7 +3127,7 @@
         <v>85</v>
       </c>
       <c r="D51" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E51" s="9">
         <v>25</v>
@@ -3133,15 +3139,15 @@
         <v>7</v>
       </c>
       <c r="H51" s="9">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I51" s="10">
         <f t="shared" si="2"/>
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="J51" s="10">
         <f t="shared" si="3"/>
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>51</v>
@@ -3156,7 +3162,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="14">
         <v>46287</v>
       </c>
@@ -3202,7 +3208,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="14">
         <v>46288</v>
       </c>
@@ -3225,15 +3231,15 @@
         <v>4</v>
       </c>
       <c r="H53" s="9">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="I53" s="10">
         <f t="shared" si="2"/>
-        <v>1025</v>
+        <v>1065</v>
       </c>
       <c r="J53" s="10">
         <f t="shared" si="3"/>
-        <v>415</v>
+        <v>375</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>56</v>
@@ -3248,7 +3254,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14">
         <v>46289</v>
       </c>
@@ -3271,15 +3277,15 @@
         <v>5</v>
       </c>
       <c r="H54" s="9">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="I54" s="10">
         <f t="shared" si="2"/>
-        <v>985</v>
+        <v>1005</v>
       </c>
       <c r="J54" s="10">
         <f t="shared" si="3"/>
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>61</v>
@@ -3294,7 +3300,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="14">
         <v>46290</v>
       </c>
@@ -3328,247 +3334,97 @@
         <v>285</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L55" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="M55" s="11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="N55" s="12" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="14">
-        <v>46291</v>
-      </c>
-      <c r="B56" s="9">
-        <v>500</v>
-      </c>
-      <c r="C56" s="9">
-        <v>80</v>
-      </c>
-      <c r="D56" s="9">
-        <v>0</v>
-      </c>
-      <c r="E56" s="9">
-        <v>0</v>
-      </c>
-      <c r="F56" s="9">
-        <v>0</v>
-      </c>
-      <c r="G56" s="9">
-        <v>0</v>
-      </c>
-      <c r="H56" s="9">
-        <v>600</v>
-      </c>
-      <c r="I56" s="10">
-        <f t="shared" si="2"/>
-        <v>1180</v>
-      </c>
-      <c r="J56" s="10">
-        <f t="shared" si="3"/>
-        <v>260</v>
-      </c>
-      <c r="K56" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L56" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M56" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="N56" s="12" t="s">
-        <v>69</v>
-      </c>
+      <c r="A56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="12"/>
     </row>
     <row r="57" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="14">
-        <v>46292</v>
-      </c>
-      <c r="B57" s="9">
-        <v>530</v>
-      </c>
-      <c r="C57" s="9">
-        <v>90</v>
-      </c>
-      <c r="D57" s="9">
-        <v>0</v>
-      </c>
-      <c r="E57" s="9">
-        <v>0</v>
-      </c>
-      <c r="F57" s="9">
-        <v>0</v>
-      </c>
-      <c r="G57" s="9">
-        <v>0</v>
-      </c>
-      <c r="H57" s="9">
-        <v>600</v>
-      </c>
-      <c r="I57" s="10">
-        <f t="shared" si="2"/>
-        <v>1220</v>
-      </c>
-      <c r="J57" s="10">
-        <f t="shared" si="3"/>
-        <v>220</v>
-      </c>
-      <c r="K57" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L57" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="M57" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N57" s="12" t="s">
-        <v>55</v>
-      </c>
+      <c r="A57" s="14"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="12"/>
     </row>
     <row r="58" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="14">
-        <v>46293</v>
-      </c>
-      <c r="B58" s="9">
-        <v>450</v>
-      </c>
-      <c r="C58" s="9">
-        <v>80</v>
-      </c>
-      <c r="D58" s="9">
-        <v>60</v>
-      </c>
-      <c r="E58" s="9">
-        <v>25</v>
-      </c>
-      <c r="F58" s="9">
-        <v>350</v>
-      </c>
-      <c r="G58" s="9">
-        <v>7</v>
-      </c>
-      <c r="H58" s="9">
-        <v>150</v>
-      </c>
-      <c r="I58" s="10">
-        <f t="shared" si="2"/>
-        <v>1115</v>
-      </c>
-      <c r="J58" s="10">
-        <f t="shared" si="3"/>
-        <v>325</v>
-      </c>
-      <c r="K58" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L58" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M58" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N58" s="12" t="s">
-        <v>60</v>
-      </c>
+      <c r="A58" s="14"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
+      <c r="N58" s="12"/>
     </row>
     <row r="59" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="14">
-        <v>46294</v>
-      </c>
-      <c r="B59" s="9">
-        <v>450</v>
-      </c>
-      <c r="C59" s="9">
-        <v>90</v>
-      </c>
-      <c r="D59" s="9">
-        <v>55</v>
-      </c>
-      <c r="E59" s="9">
-        <v>30</v>
-      </c>
-      <c r="F59" s="9">
-        <v>250</v>
-      </c>
-      <c r="G59" s="9">
-        <v>5</v>
-      </c>
-      <c r="H59" s="9">
-        <v>120</v>
-      </c>
-      <c r="I59" s="10">
-        <f t="shared" si="2"/>
-        <v>995</v>
-      </c>
-      <c r="J59" s="10">
-        <f t="shared" si="3"/>
-        <v>445</v>
-      </c>
-      <c r="K59" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L59" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M59" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N59" s="12" t="s">
-        <v>60</v>
-      </c>
+      <c r="A59" s="14"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="12"/>
     </row>
     <row r="60" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="14">
-        <v>46295</v>
-      </c>
-      <c r="B60" s="9">
-        <v>450</v>
-      </c>
-      <c r="C60" s="9">
-        <v>95</v>
-      </c>
-      <c r="D60" s="9">
-        <v>55</v>
-      </c>
-      <c r="E60" s="9">
-        <v>35</v>
-      </c>
-      <c r="F60" s="9">
-        <v>200</v>
-      </c>
-      <c r="G60" s="9">
-        <v>4</v>
-      </c>
-      <c r="H60" s="9">
-        <v>210</v>
-      </c>
-      <c r="I60" s="10">
-        <f t="shared" si="2"/>
-        <v>1045</v>
-      </c>
-      <c r="J60" s="10">
-        <f t="shared" si="3"/>
-        <v>395</v>
-      </c>
-      <c r="K60" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="L60" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M60" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="N60" s="12" t="s">
-        <v>62</v>
-      </c>
+      <c r="A60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="10"/>
+      <c r="J60" s="10"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="12"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="8"/>

--- a/12602788.xlsx
+++ b/12602788.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="47">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -153,7 +153,13 @@
     <t>Weekend routine was mostly rest,  phone and also did packing for trip.</t>
   </si>
   <si>
-    <t>Rest day, worked on a Project</t>
+    <t>Did Cardio at Gym, Studied DSA and solved Problems.</t>
+  </si>
+  <si>
+    <t>Followed daily routine, felt sad about the University Protest.</t>
+  </si>
+  <si>
+    <t>Rest day, worked on a Project.</t>
   </si>
 </sst>
 </file>
@@ -2227,11 +2233,11 @@
         <v>210</v>
       </c>
       <c r="I38" s="5">
-        <f t="shared" ref="I38:I56" si="2">IF(SUM(B38:F38,H38)=0,"",SUM(B38:F38,H38))</f>
+        <f t="shared" ref="I38:I58" si="2">IF(SUM(B38:F38,H38)=0,"",SUM(B38:F38,H38))</f>
         <v>1075</v>
       </c>
       <c r="J38" s="5">
-        <f t="shared" ref="J38:J56" si="3">IF(I38="","",1440-I38)</f>
+        <f t="shared" ref="J38:J58" si="3">IF(I38="","",1440-I38)</f>
         <v>365</v>
       </c>
       <c r="K38" s="6" t="s">
@@ -3072,40 +3078,100 @@
         <v>34</v>
       </c>
       <c r="N56" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="9">
+        <v>46292</v>
+      </c>
+      <c r="B57" s="4">
+        <v>510</v>
+      </c>
+      <c r="C57" s="4">
+        <v>90</v>
+      </c>
+      <c r="D57" s="4">
+        <v>0</v>
+      </c>
+      <c r="E57" s="4">
+        <v>50</v>
+      </c>
+      <c r="F57" s="4">
+        <v>0</v>
+      </c>
+      <c r="G57" s="4">
+        <v>0</v>
+      </c>
+      <c r="H57" s="4">
+        <v>400</v>
+      </c>
+      <c r="I57" s="5">
+        <f t="shared" si="2"/>
+        <v>1050</v>
+      </c>
+      <c r="J57" s="5">
+        <f t="shared" si="3"/>
+        <v>390</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N57" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="9">
+        <v>46293</v>
+      </c>
+      <c r="B58" s="4">
+        <v>520</v>
+      </c>
+      <c r="C58" s="4">
+        <v>95</v>
+      </c>
+      <c r="D58" s="4">
+        <v>40</v>
+      </c>
+      <c r="E58" s="4">
+        <v>40</v>
+      </c>
+      <c r="F58" s="4">
+        <v>0</v>
+      </c>
+      <c r="G58" s="4">
+        <v>0</v>
+      </c>
+      <c r="H58" s="4">
+        <v>360</v>
+      </c>
+      <c r="I58" s="5">
+        <f t="shared" si="2"/>
+        <v>1055</v>
+      </c>
+      <c r="J58" s="5">
+        <f t="shared" si="3"/>
+        <v>385</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N58" s="7" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="9"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="6"/>
-      <c r="N57" s="7"/>
-    </row>
-    <row r="58" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="9"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
-      <c r="N58" s="7"/>
     </row>
     <row r="59" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>

--- a/12602788.xlsx
+++ b/12602788.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="52">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -160,6 +160,21 @@
   </si>
   <si>
     <t>Rest day, worked on a Project.</t>
+  </si>
+  <si>
+    <t>Studied DSA and solved Problems.</t>
+  </si>
+  <si>
+    <t>Studied DSA and solved Problems on LeetCode.</t>
+  </si>
+  <si>
+    <t>Travelled out of Station,Studied DSA.</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Studied DSA and solved Problems on LeetCode and c++ on HackerRank.</t>
   </si>
 </sst>
 </file>
@@ -333,7 +348,73 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3174,84 +3255,234 @@
       </c>
     </row>
     <row r="59" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="9"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
-      <c r="N59" s="7"/>
+      <c r="A59" s="9">
+        <v>46294</v>
+      </c>
+      <c r="B59" s="4">
+        <v>500</v>
+      </c>
+      <c r="C59" s="4">
+        <v>85</v>
+      </c>
+      <c r="D59" s="4">
+        <v>50</v>
+      </c>
+      <c r="E59" s="4">
+        <v>80</v>
+      </c>
+      <c r="F59" s="4">
+        <v>0</v>
+      </c>
+      <c r="G59" s="4">
+        <v>0</v>
+      </c>
+      <c r="H59" s="4">
+        <v>350</v>
+      </c>
+      <c r="I59" s="5">
+        <f t="shared" ref="I59:I63" si="4">IF(SUM(B59:F59,H59)=0,"",SUM(B59:F59,H59))</f>
+        <v>1065</v>
+      </c>
+      <c r="J59" s="5">
+        <f t="shared" ref="J59:J63" si="5">IF(I59="","",1440-I59)</f>
+        <v>375</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L59" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M59" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N59" s="7" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="60" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="9"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
-      <c r="N60" s="7"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="3"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
-      <c r="N61" s="7"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="3"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
-      <c r="M62" s="6"/>
-      <c r="N62" s="7"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="3"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="7"/>
+      <c r="A60" s="9">
+        <v>46295</v>
+      </c>
+      <c r="B60" s="4">
+        <v>480</v>
+      </c>
+      <c r="C60" s="4">
+        <v>90</v>
+      </c>
+      <c r="D60" s="4">
+        <v>40</v>
+      </c>
+      <c r="E60" s="4">
+        <v>80</v>
+      </c>
+      <c r="F60" s="4">
+        <v>0</v>
+      </c>
+      <c r="G60" s="4">
+        <v>0</v>
+      </c>
+      <c r="H60" s="4">
+        <v>420</v>
+      </c>
+      <c r="I60" s="5">
+        <f t="shared" si="4"/>
+        <v>1110</v>
+      </c>
+      <c r="J60" s="5">
+        <f t="shared" si="5"/>
+        <v>330</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N60" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="9">
+        <v>46296</v>
+      </c>
+      <c r="B61" s="4">
+        <v>410</v>
+      </c>
+      <c r="C61" s="4">
+        <v>0</v>
+      </c>
+      <c r="D61" s="4">
+        <v>60</v>
+      </c>
+      <c r="E61" s="4">
+        <v>60</v>
+      </c>
+      <c r="F61" s="4">
+        <v>0</v>
+      </c>
+      <c r="G61" s="4">
+        <v>0</v>
+      </c>
+      <c r="H61" s="4">
+        <v>480</v>
+      </c>
+      <c r="I61" s="5">
+        <f t="shared" si="4"/>
+        <v>1010</v>
+      </c>
+      <c r="J61" s="5">
+        <f t="shared" si="5"/>
+        <v>430</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N61" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A62" s="9">
+        <v>46297</v>
+      </c>
+      <c r="B62" s="4">
+        <v>430</v>
+      </c>
+      <c r="C62" s="4">
+        <v>0</v>
+      </c>
+      <c r="D62" s="4">
+        <v>60</v>
+      </c>
+      <c r="E62" s="4">
+        <v>80</v>
+      </c>
+      <c r="F62" s="4">
+        <v>0</v>
+      </c>
+      <c r="G62" s="4">
+        <v>0</v>
+      </c>
+      <c r="H62" s="4">
+        <v>420</v>
+      </c>
+      <c r="I62" s="5">
+        <f t="shared" si="4"/>
+        <v>990</v>
+      </c>
+      <c r="J62" s="5">
+        <f t="shared" si="5"/>
+        <v>450</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N62" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="9">
+        <v>46298</v>
+      </c>
+      <c r="B63" s="4">
+        <v>440</v>
+      </c>
+      <c r="C63" s="4">
+        <v>0</v>
+      </c>
+      <c r="D63" s="4">
+        <v>60</v>
+      </c>
+      <c r="E63" s="4">
+        <v>60</v>
+      </c>
+      <c r="F63" s="4">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4">
+        <v>0</v>
+      </c>
+      <c r="H63" s="4">
+        <v>500</v>
+      </c>
+      <c r="I63" s="5">
+        <f t="shared" si="4"/>
+        <v>1060</v>
+      </c>
+      <c r="J63" s="5">
+        <f t="shared" si="5"/>
+        <v>380</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M63" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N63" s="7" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
@@ -8670,8 +8901,33 @@
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J7:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J7:J58 J64:J401">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J59">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J60">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J61">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J62">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J63">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
